--- a/IT Risk Register.xlsx
+++ b/IT Risk Register.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salmo\Desktop\Tech\03 Projects\Enterprise Network Lab\03 Governance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C26F84-9A17-4649-9297-6F5AEB7CCE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD1DC5F-B2D1-45BF-9F35-4202CBAC1695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{EE207035-1F51-4DCC-B353-2E8B956805B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE207035-1F51-4DCC-B353-2E8B956805B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Operational Risk Register" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="191">
   <si>
     <t>Risk Title</t>
   </si>
@@ -719,9 +719,6 @@
     <t>Strategic</t>
   </si>
   <si>
-    <t>If the single inter-VLAN router fails while acting as the network gateway, the network becomes vulnerable to total internal connectivity loss resulting in operational disruption.</t>
-  </si>
-  <si>
     <t>If an access switch fails without redundancy, connected departments become vulnerable to complete network isolation resulting in service disruption.</t>
   </si>
   <si>
@@ -755,9 +752,6 @@
     <t>If infrastructure documentation is missing or incomplete, recovery operations become vulnerable to delays resulting in prolonged outages.</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>IT Infrastructure Manager</t>
   </si>
   <si>
@@ -843,12 +837,45 @@
   </si>
   <si>
     <t>Design and Implement an In-House Network Monitoring Capability</t>
+  </si>
+  <si>
+    <t>Centralized, auditable change management system</t>
+  </si>
+  <si>
+    <t>If the single core router fails while providing inter-VLAN routing, inter-campus connectivity, and DHCP relay services, the network risks widespread cross-site communication failure and loss of critical services, resulting in operational disruption.</t>
+  </si>
+  <si>
+    <t>Manual failover using router substitution for Campus A recovery and degraded standalone operation for Campus B including manual IP configuration and local service provisioning</t>
+  </si>
+  <si>
+    <t>Maintain operational continuity during router failure by enabling Campus B standalone operation, pre-staging critical data locally, and supporting rapid recovery of Campus A through hardware reallocation.</t>
+  </si>
+  <si>
+    <t>Eliminate single points of failure by implementing redundant routing and dual-site service capability with replicated infrastructure.</t>
+  </si>
+  <si>
+    <t>Implement and validate manual failover procedures including router substitution for Campus A recovery and degraded standalone operation for Campus B with manual IP configuration and local service activation</t>
+  </si>
+  <si>
+    <t>Change Management Policy v1.0</t>
+  </si>
+  <si>
+    <t>Implement Change Management Procedure v1.0 (aligned to Change Management Policy v1.0)</t>
+  </si>
+  <si>
+    <t>Achieved – Formal change management process established</t>
+  </si>
+  <si>
+    <t>Develop a centralized application to automate and improve implementation of the change control policy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -900,7 +927,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -910,6 +937,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1100,7 +1139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1138,23 +1177,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1162,10 +1189,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1188,6 +1242,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1571,86 +1631,86 @@
     <col min="11" max="11" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="55.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="67.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="59.85546875" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="46.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="48.140625" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="33.85546875" style="4" customWidth="1"/>
     <col min="20" max="20" width="51.140625" style="5" customWidth="1"/>
-    <col min="21" max="21" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" style="20" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="19.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19.42578125" style="21" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="27" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="28"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="25" t="s">
+      <c r="J1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="25" t="s">
+      <c r="N1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="25" t="s">
+      <c r="R1" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="S1" s="25" t="s">
+      <c r="S1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="T1" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="29"/>
-      <c r="V1" s="21" t="s">
+      <c r="U1" s="34"/>
+      <c r="V1" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="W1" s="21" t="s">
+      <c r="W1" s="26" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="22"/>
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="25"/>
       <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1669,100 +1729,100 @@
       <c r="K2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
       <c r="T2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="U2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="27"/>
     </row>
     <row r="3" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="E3" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="13">
         <v>4</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="13">
         <v>4</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="13">
         <f t="shared" ref="H3:H14" si="0">F3*G3</f>
         <v>16</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="13">
         <v>4</v>
       </c>
-      <c r="J3" s="2">
-        <v>2</v>
-      </c>
-      <c r="K3" s="2">
+      <c r="J3" s="13">
+        <v>4</v>
+      </c>
+      <c r="K3" s="13">
         <f t="shared" ref="K3:K14" si="1">I3*J3</f>
-        <v>8</v>
-      </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2">
+        <v>16</v>
+      </c>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13">
         <v>1</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="N3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="T3" s="3" t="s">
+      <c r="O3" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="U3" s="13">
-        <v>46419</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="W3" s="13">
-        <v>46113</v>
+      <c r="P3" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="T3" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="U3" s="35">
+        <v>46132</v>
+      </c>
+      <c r="V3" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="W3" s="17">
+        <v>46133</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>137</v>
@@ -1771,7 +1831,7 @@
         <v>139</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F4" s="6">
         <v>4</v>
@@ -1784,120 +1844,136 @@
         <v>16</v>
       </c>
       <c r="I4" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6">
         <v>2</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="O4" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>189</v>
       </c>
       <c r="Q4" s="6" t="s">
         <v>181</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="S4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="U4" s="17">
+        <v>46147</v>
+      </c>
+      <c r="V4" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="W4" s="18">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="U4" s="14">
-        <v>46120</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="W4" s="14">
-        <v>46120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" s="15">
-        <v>4</v>
-      </c>
-      <c r="G5" s="15">
-        <v>4</v>
-      </c>
-      <c r="H5" s="15">
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="I5" s="15">
-        <v>4</v>
-      </c>
-      <c r="J5" s="15">
-        <v>4</v>
-      </c>
-      <c r="K5" s="15">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5</v>
+      </c>
+      <c r="K5" s="2">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="17"/>
-      <c r="V5" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="W5" s="17">
-        <v>46089</v>
+      <c r="N5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="P5" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="T5" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="U5" s="19">
+        <v>46140</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W5" s="19">
+        <v>46133</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F6" s="4">
         <v>3</v>
@@ -1922,75 +1998,74 @@
       <c r="M6" s="4">
         <v>4</v>
       </c>
-      <c r="U6" s="18"/>
       <c r="V6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="W6" s="18">
+        <v>154</v>
+      </c>
+      <c r="W6" s="20">
         <v>46089</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="A7" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="E7" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="13">
         <v>3</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="13">
+        <v>4</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="I7" s="13">
+        <v>3</v>
+      </c>
+      <c r="J7" s="13">
+        <v>4</v>
+      </c>
+      <c r="K7" s="13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13">
         <v>5</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="I7" s="2">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>5</v>
-      </c>
-      <c r="K7" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2">
-        <v>5</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="W7" s="13">
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="W7" s="17">
         <v>46089</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>136</v>
@@ -1999,7 +2074,7 @@
         <v>139</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F8" s="6">
         <v>3</v>
@@ -2032,84 +2107,84 @@
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="7"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="18"/>
       <c r="V8" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="W8" s="14">
+        <v>154</v>
+      </c>
+      <c r="W8" s="18">
         <v>46089</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="2">
         <v>4</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="2">
         <v>3</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="2">
         <v>4</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="2">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2">
         <v>7</v>
       </c>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="W9" s="17">
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W9" s="19">
         <v>46089</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F10" s="4">
         <v>3</v>
@@ -2134,232 +2209,232 @@
       <c r="M10" s="4">
         <v>8</v>
       </c>
-      <c r="U10" s="18"/>
       <c r="V10" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="W10" s="18">
+        <v>154</v>
+      </c>
+      <c r="W10" s="20">
         <v>46089</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="A11" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="13">
         <v>3</v>
       </c>
-      <c r="G11" s="2">
-        <v>4</v>
-      </c>
-      <c r="H11" s="2">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="G11" s="13">
         <v>3</v>
       </c>
-      <c r="J11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" s="2">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2">
-        <v>9</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="W11" s="13">
-        <v>46089</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F12" s="6">
-        <v>3</v>
-      </c>
-      <c r="G12" s="6">
-        <v>3</v>
-      </c>
-      <c r="H12" s="6">
+      <c r="H11" s="13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I11" s="13">
         <v>3</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J11" s="13">
         <v>3</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K11" s="13">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6">
-        <v>10</v>
-      </c>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="14"/>
-      <c r="V12" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="W12" s="14">
+      <c r="L11" s="13"/>
+      <c r="M11" s="13">
+        <v>9</v>
+      </c>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="W11" s="17">
         <v>46089</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="12" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="E12" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="4">
         <v>3</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G12" s="4">
         <v>3</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H12" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I12" s="4">
         <v>3</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J12" s="4">
         <v>3</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K12" s="4">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2">
-        <v>11</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="W13" s="13">
+      <c r="M12" s="4">
+        <v>10</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="W12" s="20">
         <v>46089</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="13" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B13" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C13" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D13" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="E13" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" s="13">
         <v>3</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G13" s="13">
         <v>3</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H13" s="13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I13" s="13">
         <v>3</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J13" s="13">
         <v>3</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K13" s="13">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6" t="s">
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="W13" s="17">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F14" s="4">
+        <v>4</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="I14" s="4">
+        <v>4</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="R14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="W14" s="14">
-        <v>46089</v>
+      <c r="S14" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="U14" s="20">
+        <v>46419</v>
+      </c>
+      <c r="V14" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="W14" s="20">
+        <v>46113</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
@@ -2385,9 +2460,9 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="2"/>
+      <c r="U15" s="19"/>
       <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
+      <c r="W15" s="19"/>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -2412,9 +2487,9 @@
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="7"/>
-      <c r="U16" s="6"/>
+      <c r="U16" s="18"/>
       <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
+      <c r="W16" s="18"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -2439,9 +2514,9 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="2"/>
+      <c r="U17" s="19"/>
       <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
+      <c r="W17" s="19"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
@@ -2466,9 +2541,9 @@
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
       <c r="T18" s="7"/>
-      <c r="U18" s="6"/>
+      <c r="U18" s="18"/>
       <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
+      <c r="W18" s="18"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -2493,9 +2568,9 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="2"/>
+      <c r="U19" s="19"/>
       <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
+      <c r="W19" s="19"/>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -2520,9 +2595,9 @@
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
       <c r="T20" s="7"/>
-      <c r="U20" s="6"/>
+      <c r="U20" s="18"/>
       <c r="V20" s="6"/>
-      <c r="W20" s="6"/>
+      <c r="W20" s="18"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -2547,9 +2622,9 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="2"/>
+      <c r="U21" s="19"/>
       <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
+      <c r="W21" s="19"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -2574,9 +2649,9 @@
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
       <c r="T22" s="7"/>
-      <c r="U22" s="6"/>
+      <c r="U22" s="18"/>
       <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
+      <c r="W22" s="18"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
@@ -2601,9 +2676,9 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="2"/>
+      <c r="U23" s="19"/>
       <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
+      <c r="W23" s="19"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
@@ -2628,9 +2703,9 @@
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="7"/>
-      <c r="U24" s="6"/>
+      <c r="U24" s="18"/>
       <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
+      <c r="W24" s="18"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
@@ -2655,9 +2730,9 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="2"/>
+      <c r="U25" s="19"/>
       <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
+      <c r="W25" s="19"/>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
@@ -2682,9 +2757,9 @@
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
       <c r="T26" s="7"/>
-      <c r="U26" s="6"/>
+      <c r="U26" s="18"/>
       <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
+      <c r="W26" s="18"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
@@ -2709,9 +2784,9 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="2"/>
+      <c r="U27" s="19"/>
       <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
+      <c r="W27" s="19"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -2736,9 +2811,9 @@
       <c r="R28" s="6"/>
       <c r="S28" s="6"/>
       <c r="T28" s="7"/>
-      <c r="U28" s="6"/>
+      <c r="U28" s="18"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
+      <c r="W28" s="18"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
@@ -2763,9 +2838,9 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="2"/>
+      <c r="U29" s="19"/>
       <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
+      <c r="W29" s="19"/>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
@@ -2790,9 +2865,9 @@
       <c r="R30" s="6"/>
       <c r="S30" s="6"/>
       <c r="T30" s="7"/>
-      <c r="U30" s="6"/>
+      <c r="U30" s="18"/>
       <c r="V30" s="6"/>
-      <c r="W30" s="6"/>
+      <c r="W30" s="18"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
@@ -2817,9 +2892,9 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="2"/>
+      <c r="U31" s="19"/>
       <c r="V31" s="2"/>
-      <c r="W31" s="2"/>
+      <c r="W31" s="19"/>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
@@ -2844,9 +2919,9 @@
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
       <c r="T32" s="7"/>
-      <c r="U32" s="6"/>
+      <c r="U32" s="18"/>
       <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
+      <c r="W32" s="18"/>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
@@ -2871,9 +2946,9 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="2"/>
+      <c r="U33" s="19"/>
       <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
+      <c r="W33" s="19"/>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
@@ -2898,9 +2973,9 @@
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
       <c r="T34" s="7"/>
-      <c r="U34" s="6"/>
+      <c r="U34" s="18"/>
       <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
+      <c r="W34" s="18"/>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
@@ -2925,9 +3000,9 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="2"/>
+      <c r="U35" s="19"/>
       <c r="V35" s="2"/>
-      <c r="W35" s="2"/>
+      <c r="W35" s="19"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
@@ -2952,9 +3027,9 @@
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
       <c r="T36" s="7"/>
-      <c r="U36" s="6"/>
+      <c r="U36" s="18"/>
       <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
+      <c r="W36" s="18"/>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
@@ -2979,9 +3054,9 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="2"/>
+      <c r="U37" s="19"/>
       <c r="V37" s="2"/>
-      <c r="W37" s="2"/>
+      <c r="W37" s="19"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
@@ -3006,9 +3081,9 @@
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
       <c r="T38" s="7"/>
-      <c r="U38" s="6"/>
+      <c r="U38" s="18"/>
       <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
+      <c r="W38" s="18"/>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
@@ -3033,9 +3108,9 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="2"/>
+      <c r="U39" s="19"/>
       <c r="V39" s="2"/>
-      <c r="W39" s="2"/>
+      <c r="W39" s="19"/>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
@@ -3060,9 +3135,9 @@
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
       <c r="T40" s="7"/>
-      <c r="U40" s="6"/>
+      <c r="U40" s="18"/>
       <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
+      <c r="W40" s="18"/>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
@@ -3087,9 +3162,9 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="2"/>
+      <c r="U41" s="19"/>
       <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
+      <c r="W41" s="19"/>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
@@ -3114,9 +3189,9 @@
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
       <c r="T42" s="7"/>
-      <c r="U42" s="6"/>
+      <c r="U42" s="18"/>
       <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
+      <c r="W42" s="18"/>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
@@ -3141,9 +3216,9 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="2"/>
+      <c r="U43" s="19"/>
       <c r="V43" s="2"/>
-      <c r="W43" s="2"/>
+      <c r="W43" s="19"/>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
@@ -3168,9 +3243,9 @@
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
       <c r="T44" s="7"/>
-      <c r="U44" s="6"/>
+      <c r="U44" s="18"/>
       <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
+      <c r="W44" s="18"/>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
@@ -3195,9 +3270,9 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="2"/>
+      <c r="U45" s="19"/>
       <c r="V45" s="2"/>
-      <c r="W45" s="2"/>
+      <c r="W45" s="19"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
@@ -3222,9 +3297,9 @@
       <c r="R46" s="6"/>
       <c r="S46" s="6"/>
       <c r="T46" s="7"/>
-      <c r="U46" s="6"/>
+      <c r="U46" s="18"/>
       <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
+      <c r="W46" s="18"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -3249,9 +3324,9 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="2"/>
+      <c r="U47" s="19"/>
       <c r="V47" s="2"/>
-      <c r="W47" s="2"/>
+      <c r="W47" s="19"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
@@ -3276,9 +3351,9 @@
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
       <c r="T48" s="7"/>
-      <c r="U48" s="6"/>
+      <c r="U48" s="18"/>
       <c r="V48" s="6"/>
-      <c r="W48" s="6"/>
+      <c r="W48" s="18"/>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
@@ -3303,9 +3378,9 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="2"/>
+      <c r="U49" s="19"/>
       <c r="V49" s="2"/>
-      <c r="W49" s="2"/>
+      <c r="W49" s="19"/>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
@@ -3330,9 +3405,9 @@
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
       <c r="T50" s="7"/>
-      <c r="U50" s="6"/>
+      <c r="U50" s="18"/>
       <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
+      <c r="W50" s="18"/>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
@@ -3357,9 +3432,9 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="2"/>
+      <c r="U51" s="19"/>
       <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
+      <c r="W51" s="19"/>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
@@ -3384,9 +3459,9 @@
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="7"/>
-      <c r="U52" s="6"/>
+      <c r="U52" s="18"/>
       <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
+      <c r="W52" s="18"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
@@ -3411,9 +3486,9 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="2"/>
+      <c r="U53" s="19"/>
       <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
+      <c r="W53" s="19"/>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
@@ -3438,9 +3513,9 @@
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
       <c r="T54" s="7"/>
-      <c r="U54" s="6"/>
+      <c r="U54" s="18"/>
       <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
+      <c r="W54" s="18"/>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
@@ -3465,9 +3540,9 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="2"/>
+      <c r="U55" s="19"/>
       <c r="V55" s="2"/>
-      <c r="W55" s="2"/>
+      <c r="W55" s="19"/>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
@@ -3492,9 +3567,9 @@
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
       <c r="T56" s="7"/>
-      <c r="U56" s="6"/>
+      <c r="U56" s="18"/>
       <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
+      <c r="W56" s="18"/>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
@@ -3519,9 +3594,9 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="3"/>
-      <c r="U57" s="2"/>
+      <c r="U57" s="19"/>
       <c r="V57" s="2"/>
-      <c r="W57" s="2"/>
+      <c r="W57" s="19"/>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
@@ -3546,9 +3621,9 @@
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
       <c r="T58" s="7"/>
-      <c r="U58" s="6"/>
+      <c r="U58" s="18"/>
       <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
+      <c r="W58" s="18"/>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
@@ -3573,9 +3648,9 @@
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="3"/>
-      <c r="U59" s="2"/>
+      <c r="U59" s="19"/>
       <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
+      <c r="W59" s="19"/>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
@@ -3600,9 +3675,9 @@
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
       <c r="T60" s="7"/>
-      <c r="U60" s="6"/>
+      <c r="U60" s="18"/>
       <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
+      <c r="W60" s="18"/>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
@@ -3627,9 +3702,9 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="3"/>
-      <c r="U61" s="2"/>
+      <c r="U61" s="19"/>
       <c r="V61" s="2"/>
-      <c r="W61" s="2"/>
+      <c r="W61" s="19"/>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
@@ -3654,9 +3729,9 @@
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
       <c r="T62" s="7"/>
-      <c r="U62" s="6"/>
+      <c r="U62" s="18"/>
       <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
+      <c r="W62" s="18"/>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
@@ -3681,9 +3756,9 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="3"/>
-      <c r="U63" s="2"/>
+      <c r="U63" s="19"/>
       <c r="V63" s="2"/>
-      <c r="W63" s="2"/>
+      <c r="W63" s="19"/>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
@@ -3708,9 +3783,9 @@
       <c r="R64" s="6"/>
       <c r="S64" s="6"/>
       <c r="T64" s="7"/>
-      <c r="U64" s="6"/>
+      <c r="U64" s="18"/>
       <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
+      <c r="W64" s="18"/>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
@@ -3735,9 +3810,9 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="3"/>
-      <c r="U65" s="2"/>
+      <c r="U65" s="19"/>
       <c r="V65" s="2"/>
-      <c r="W65" s="2"/>
+      <c r="W65" s="19"/>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
@@ -3762,9 +3837,9 @@
       <c r="R66" s="6"/>
       <c r="S66" s="6"/>
       <c r="T66" s="7"/>
-      <c r="U66" s="6"/>
+      <c r="U66" s="18"/>
       <c r="V66" s="6"/>
-      <c r="W66" s="6"/>
+      <c r="W66" s="18"/>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
@@ -3789,9 +3864,9 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="2"/>
+      <c r="U67" s="19"/>
       <c r="V67" s="2"/>
-      <c r="W67" s="2"/>
+      <c r="W67" s="19"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
@@ -3816,9 +3891,9 @@
       <c r="R68" s="6"/>
       <c r="S68" s="6"/>
       <c r="T68" s="7"/>
-      <c r="U68" s="6"/>
+      <c r="U68" s="18"/>
       <c r="V68" s="6"/>
-      <c r="W68" s="6"/>
+      <c r="W68" s="18"/>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
@@ -3843,9 +3918,9 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
       <c r="T69" s="3"/>
-      <c r="U69" s="2"/>
+      <c r="U69" s="19"/>
       <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
+      <c r="W69" s="19"/>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
@@ -3870,9 +3945,9 @@
       <c r="R70" s="6"/>
       <c r="S70" s="6"/>
       <c r="T70" s="7"/>
-      <c r="U70" s="6"/>
+      <c r="U70" s="18"/>
       <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
+      <c r="W70" s="18"/>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
@@ -3897,9 +3972,9 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
       <c r="T71" s="3"/>
-      <c r="U71" s="2"/>
+      <c r="U71" s="19"/>
       <c r="V71" s="2"/>
-      <c r="W71" s="2"/>
+      <c r="W71" s="19"/>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
@@ -3924,9 +3999,9 @@
       <c r="R72" s="6"/>
       <c r="S72" s="6"/>
       <c r="T72" s="7"/>
-      <c r="U72" s="6"/>
+      <c r="U72" s="18"/>
       <c r="V72" s="6"/>
-      <c r="W72" s="6"/>
+      <c r="W72" s="18"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
@@ -3951,9 +4026,9 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="3"/>
-      <c r="U73" s="2"/>
+      <c r="U73" s="19"/>
       <c r="V73" s="2"/>
-      <c r="W73" s="2"/>
+      <c r="W73" s="19"/>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
@@ -3978,9 +4053,9 @@
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
       <c r="T74" s="7"/>
-      <c r="U74" s="6"/>
+      <c r="U74" s="18"/>
       <c r="V74" s="6"/>
-      <c r="W74" s="6"/>
+      <c r="W74" s="18"/>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
@@ -4005,9 +4080,9 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
       <c r="T75" s="3"/>
-      <c r="U75" s="2"/>
+      <c r="U75" s="19"/>
       <c r="V75" s="2"/>
-      <c r="W75" s="2"/>
+      <c r="W75" s="19"/>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
@@ -4032,9 +4107,9 @@
       <c r="R76" s="6"/>
       <c r="S76" s="6"/>
       <c r="T76" s="7"/>
-      <c r="U76" s="6"/>
+      <c r="U76" s="18"/>
       <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
+      <c r="W76" s="18"/>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
@@ -4059,9 +4134,9 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
       <c r="T77" s="3"/>
-      <c r="U77" s="2"/>
+      <c r="U77" s="19"/>
       <c r="V77" s="2"/>
-      <c r="W77" s="2"/>
+      <c r="W77" s="19"/>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
@@ -4086,9 +4161,9 @@
       <c r="R78" s="6"/>
       <c r="S78" s="6"/>
       <c r="T78" s="7"/>
-      <c r="U78" s="6"/>
+      <c r="U78" s="18"/>
       <c r="V78" s="6"/>
-      <c r="W78" s="6"/>
+      <c r="W78" s="18"/>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
@@ -4113,9 +4188,9 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
       <c r="T79" s="3"/>
-      <c r="U79" s="2"/>
+      <c r="U79" s="19"/>
       <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
+      <c r="W79" s="19"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
@@ -4140,9 +4215,9 @@
       <c r="R80" s="6"/>
       <c r="S80" s="6"/>
       <c r="T80" s="7"/>
-      <c r="U80" s="6"/>
+      <c r="U80" s="18"/>
       <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
+      <c r="W80" s="18"/>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
@@ -4167,9 +4242,9 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
       <c r="T81" s="3"/>
-      <c r="U81" s="2"/>
+      <c r="U81" s="19"/>
       <c r="V81" s="2"/>
-      <c r="W81" s="2"/>
+      <c r="W81" s="19"/>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
@@ -4194,9 +4269,9 @@
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
       <c r="T82" s="7"/>
-      <c r="U82" s="6"/>
+      <c r="U82" s="18"/>
       <c r="V82" s="6"/>
-      <c r="W82" s="6"/>
+      <c r="W82" s="18"/>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
@@ -4221,9 +4296,9 @@
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
       <c r="T83" s="3"/>
-      <c r="U83" s="2"/>
+      <c r="U83" s="19"/>
       <c r="V83" s="2"/>
-      <c r="W83" s="2"/>
+      <c r="W83" s="19"/>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
@@ -4248,9 +4323,9 @@
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
       <c r="T84" s="7"/>
-      <c r="U84" s="6"/>
+      <c r="U84" s="18"/>
       <c r="V84" s="6"/>
-      <c r="W84" s="6"/>
+      <c r="W84" s="18"/>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
@@ -4275,9 +4350,9 @@
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
       <c r="T85" s="3"/>
-      <c r="U85" s="2"/>
+      <c r="U85" s="19"/>
       <c r="V85" s="2"/>
-      <c r="W85" s="2"/>
+      <c r="W85" s="19"/>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
@@ -4302,9 +4377,9 @@
       <c r="R86" s="6"/>
       <c r="S86" s="6"/>
       <c r="T86" s="7"/>
-      <c r="U86" s="6"/>
+      <c r="U86" s="18"/>
       <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
+      <c r="W86" s="18"/>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
@@ -4329,9 +4404,9 @@
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
       <c r="T87" s="3"/>
-      <c r="U87" s="2"/>
+      <c r="U87" s="19"/>
       <c r="V87" s="2"/>
-      <c r="W87" s="2"/>
+      <c r="W87" s="19"/>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
@@ -4356,9 +4431,9 @@
       <c r="R88" s="6"/>
       <c r="S88" s="6"/>
       <c r="T88" s="7"/>
-      <c r="U88" s="6"/>
+      <c r="U88" s="18"/>
       <c r="V88" s="6"/>
-      <c r="W88" s="6"/>
+      <c r="W88" s="18"/>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
@@ -4383,9 +4458,9 @@
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
       <c r="T89" s="3"/>
-      <c r="U89" s="2"/>
+      <c r="U89" s="19"/>
       <c r="V89" s="2"/>
-      <c r="W89" s="2"/>
+      <c r="W89" s="19"/>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
@@ -4410,9 +4485,9 @@
       <c r="R90" s="6"/>
       <c r="S90" s="6"/>
       <c r="T90" s="7"/>
-      <c r="U90" s="6"/>
+      <c r="U90" s="18"/>
       <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
+      <c r="W90" s="18"/>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
@@ -4437,9 +4512,9 @@
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
       <c r="T91" s="3"/>
-      <c r="U91" s="2"/>
+      <c r="U91" s="19"/>
       <c r="V91" s="2"/>
-      <c r="W91" s="2"/>
+      <c r="W91" s="19"/>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
@@ -4464,9 +4539,9 @@
       <c r="R92" s="6"/>
       <c r="S92" s="6"/>
       <c r="T92" s="7"/>
-      <c r="U92" s="6"/>
+      <c r="U92" s="18"/>
       <c r="V92" s="6"/>
-      <c r="W92" s="6"/>
+      <c r="W92" s="18"/>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
@@ -4491,9 +4566,9 @@
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
       <c r="T93" s="3"/>
-      <c r="U93" s="2"/>
+      <c r="U93" s="19"/>
       <c r="V93" s="2"/>
-      <c r="W93" s="2"/>
+      <c r="W93" s="19"/>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
@@ -4518,9 +4593,9 @@
       <c r="R94" s="6"/>
       <c r="S94" s="6"/>
       <c r="T94" s="7"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="18"/>
       <c r="V94" s="6"/>
-      <c r="W94" s="6"/>
+      <c r="W94" s="18"/>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
@@ -4545,9 +4620,9 @@
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="2"/>
+      <c r="U95" s="19"/>
       <c r="V95" s="2"/>
-      <c r="W95" s="2"/>
+      <c r="W95" s="19"/>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
@@ -4572,9 +4647,9 @@
       <c r="R96" s="6"/>
       <c r="S96" s="6"/>
       <c r="T96" s="7"/>
-      <c r="U96" s="6"/>
+      <c r="U96" s="18"/>
       <c r="V96" s="6"/>
-      <c r="W96" s="6"/>
+      <c r="W96" s="18"/>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
@@ -4599,9 +4674,9 @@
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
       <c r="T97" s="3"/>
-      <c r="U97" s="2"/>
+      <c r="U97" s="19"/>
       <c r="V97" s="2"/>
-      <c r="W97" s="2"/>
+      <c r="W97" s="19"/>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
@@ -4626,9 +4701,9 @@
       <c r="R98" s="6"/>
       <c r="S98" s="6"/>
       <c r="T98" s="7"/>
-      <c r="U98" s="6"/>
+      <c r="U98" s="18"/>
       <c r="V98" s="6"/>
-      <c r="W98" s="6"/>
+      <c r="W98" s="18"/>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
@@ -4653,9 +4728,9 @@
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
       <c r="T99" s="3"/>
-      <c r="U99" s="2"/>
+      <c r="U99" s="19"/>
       <c r="V99" s="2"/>
-      <c r="W99" s="2"/>
+      <c r="W99" s="19"/>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
@@ -4680,9 +4755,9 @@
       <c r="R100" s="6"/>
       <c r="S100" s="6"/>
       <c r="T100" s="7"/>
-      <c r="U100" s="6"/>
+      <c r="U100" s="18"/>
       <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
+      <c r="W100" s="18"/>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
@@ -4707,9 +4782,9 @@
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
       <c r="T101" s="3"/>
-      <c r="U101" s="2"/>
+      <c r="U101" s="19"/>
       <c r="V101" s="2"/>
-      <c r="W101" s="2"/>
+      <c r="W101" s="19"/>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
@@ -4734,13 +4809,13 @@
       <c r="R102" s="6"/>
       <c r="S102" s="6"/>
       <c r="T102" s="7"/>
-      <c r="U102" s="6"/>
+      <c r="U102" s="18"/>
       <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
+      <c r="W102" s="18"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:W102">
-    <sortCondition descending="1" ref="K3:K102"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:W14">
+    <sortCondition descending="1" ref="K3:K14"/>
   </sortState>
   <mergeCells count="18">
     <mergeCell ref="A1:A2"/>
@@ -4839,23 +4914,23 @@
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="1:6" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E1" s="19" t="s">
+      <c r="C1" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="15" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4866,17 +4941,17 @@
       <c r="B2" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -4884,19 +4959,19 @@
         <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" s="20">
+        <v>161</v>
+      </c>
+      <c r="C3" s="16">
         <v>2</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -4904,49 +4979,49 @@
         <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="20">
+        <v>162</v>
+      </c>
+      <c r="C4" s="16">
         <v>3</v>
       </c>
       <c r="D4">
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="20">
+        <v>163</v>
+      </c>
+      <c r="C5" s="16">
         <v>4</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="16">
         <v>5</v>
       </c>
       <c r="D6">
@@ -4954,22 +5029,22 @@
       </c>
       <c r="E6"/>
       <c r="F6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/IT Risk Register.xlsx
+++ b/IT Risk Register.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salmo\Desktop\Tech\03 Projects\Enterprise Network Lab\03 Governance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD1DC5F-B2D1-45BF-9F35-4202CBAC1695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF72125-A52C-4687-B53D-CA2BEE59F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE207035-1F51-4DCC-B353-2E8B956805B3}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{EE207035-1F51-4DCC-B353-2E8B956805B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Operational Risk Register" sheetId="1" r:id="rId1"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="196">
   <si>
     <t>Risk Title</t>
   </si>
@@ -867,6 +867,21 @@
   </si>
   <si>
     <t>Develop a centralized application to automate and improve implementation of the change control policy</t>
+  </si>
+  <si>
+    <t>Implement device-specific administrative and privileged (enable) passwords as an interim containment measure. Restrict credential distribution to authorised personnel based on operational need, reducing unauthorized access and limiting exposure until formal identity-based access controls are implemented.</t>
+  </si>
+  <si>
+    <t>Relocate network devices to the most secure available offices within each floor, building, and campus. Restrict physical access by securing rooms with locked doors and implementing controlled key access under third-party supervision, requiring formal sign-out and return procedures. Re-route cabling as required to support relocation and ensure devices are not accessible from unsecured or public areas.</t>
+  </si>
+  <si>
+    <t>Deploy dedicated secure network infrastructure areas using locked racks within controlled-access rooms. Implement RFID-based access control with centralised management, environmental protections (fire suppression and climate control), and integrated monitoring systems to ensure all physical and administrative access is restricted, logged, and auditable.</t>
+  </si>
+  <si>
+    <t>Configure secure administrative access on all network devices by setting unique device-level and privileged (enable) passwords, removing default credentials, and restricting access to authorised personnel only.</t>
+  </si>
+  <si>
+    <t>Configure secure administrative access on all network devices by implementing unique device-level and privileged (enable) passwords, removing default credentials, and restricting access to authorised personnel.</t>
   </si>
 </sst>
 </file>
@@ -1210,10 +1225,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,32 +1261,8 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1632,9 +1647,9 @@
     <col min="12" max="12" width="19.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="67.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="59.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="48.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="63" style="4" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="4" customWidth="1"/>
+    <col min="17" max="17" width="58.5703125" style="4" customWidth="1"/>
     <col min="18" max="18" width="30" style="4" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="33.85546875" style="4" customWidth="1"/>
     <col min="20" max="20" width="51.140625" style="5" customWidth="1"/>
@@ -1645,72 +1660,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="33"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="32" t="s">
+      <c r="G1" s="36"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="30" t="s">
+      <c r="J1" s="36"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="M1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="N1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="O1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="P1" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="Q1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="S1" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="32" t="s">
+      <c r="T1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="24" t="s">
+      <c r="U1" s="31"/>
+      <c r="V1" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="W1" s="34" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="25"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1729,22 +1744,22 @@
       <c r="K2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
       <c r="T2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="U2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="25"/>
-      <c r="W2" s="27"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="35"/>
     </row>
     <row r="3" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
@@ -1807,7 +1822,7 @@
       <c r="T3" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="U3" s="35">
+      <c r="U3" s="24">
         <v>46132</v>
       </c>
       <c r="V3" s="13" t="s">
@@ -1863,7 +1878,7 @@
       <c r="O4" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="25" t="s">
         <v>189</v>
       </c>
       <c r="Q4" s="6" t="s">
@@ -1959,7 +1974,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="126" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>26</v>
       </c>
@@ -1986,23 +2001,47 @@
         <v>15</v>
       </c>
       <c r="I6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4">
         <v>5</v>
       </c>
       <c r="K6" s="4">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M6" s="4">
         <v>4</v>
       </c>
+      <c r="N6" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="P6" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="U6" s="20">
+        <v>46147</v>
+      </c>
       <c r="V6" s="4" t="s">
         <v>154</v>
       </c>
       <c r="W6" s="20">
-        <v>46089</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4818,6 +4857,12 @@
     <sortCondition descending="1" ref="K3:K14"/>
   </sortState>
   <mergeCells count="18">
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:E2"/>
@@ -4830,12 +4875,6 @@
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="L3:L1048576">

--- a/IT Risk Register.xlsx
+++ b/IT Risk Register.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salmo\Desktop\Tech\03 Projects\Enterprise Network Lab\03 Governance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF72125-A52C-4687-B53D-CA2BEE59F921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1059A75-F826-4CA2-8391-2F427C6A1B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{EE207035-1F51-4DCC-B353-2E8B956805B3}"/>
   </bookViews>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="216">
   <si>
     <t>Risk Title</t>
   </si>
@@ -824,39 +824,15 @@
     <t xml:space="preserve">Annual review </t>
   </si>
   <si>
-    <t>Network Operational Verification Policy v1.0</t>
-  </si>
-  <si>
-    <t>Network Operational Verification Procedure v1.0</t>
-  </si>
-  <si>
-    <t>Implement basic network monitoring capability</t>
-  </si>
-  <si>
     <t>Centralized network monitoring and alerting platform</t>
   </si>
   <si>
-    <t>Design and Implement an In-House Network Monitoring Capability</t>
-  </si>
-  <si>
     <t>Centralized, auditable change management system</t>
   </si>
   <si>
     <t>If the single core router fails while providing inter-VLAN routing, inter-campus connectivity, and DHCP relay services, the network risks widespread cross-site communication failure and loss of critical services, resulting in operational disruption.</t>
   </si>
   <si>
-    <t>Manual failover using router substitution for Campus A recovery and degraded standalone operation for Campus B including manual IP configuration and local service provisioning</t>
-  </si>
-  <si>
-    <t>Maintain operational continuity during router failure by enabling Campus B standalone operation, pre-staging critical data locally, and supporting rapid recovery of Campus A through hardware reallocation.</t>
-  </si>
-  <si>
-    <t>Eliminate single points of failure by implementing redundant routing and dual-site service capability with replicated infrastructure.</t>
-  </si>
-  <si>
-    <t>Implement and validate manual failover procedures including router substitution for Campus A recovery and degraded standalone operation for Campus B with manual IP configuration and local service activation</t>
-  </si>
-  <si>
     <t>Change Management Policy v1.0</t>
   </si>
   <si>
@@ -882,6 +858,146 @@
   </si>
   <si>
     <t>Configure secure administrative access on all network devices by implementing unique device-level and privileged (enable) passwords, removing default credentials, and restricting access to authorised personnel.</t>
+  </si>
+  <si>
+    <t>In-house automated network health monitoring implemented per Network Operational Verification Policy v1.0, reducing likelihood of undetected network failures.</t>
+  </si>
+  <si>
+    <t>Use monitoring system in accordance with Network Operational Verification Policy v1.0.</t>
+  </si>
+  <si>
+    <t>Achieved – Monitoring capability implemented; funding required for alerting and centralised visibility.</t>
+  </si>
+  <si>
+    <t>Propose third-party monitoring solutions for approval at the next executive meeting.</t>
+  </si>
+  <si>
+    <t>Implementation of a formal Business Continuity Policy and Procedure (v1.0), including a defined router failure response (BCP-001), enabling structured failover, controlled degraded operation, and reduced operational impact during failure events.</t>
+  </si>
+  <si>
+    <t>Execute BCP-001 for controlled failover and recovery during router failure.</t>
+  </si>
+  <si>
+    <t>Achieved – BCP implemented; funding required for redundancy.</t>
+  </si>
+  <si>
+    <t>Unauthorised Physical Access to Critical Infrastructure</t>
+  </si>
+  <si>
+    <t>Weak or ineffective physical access controls, including tailgating and lack of identity enforcement, allow unauthorised individuals to gain access to controlled areas and interact with critical infrastructure, enabling system compromise, disruption, or unauthorised changes.</t>
+  </si>
+  <si>
+    <t>Unauthorised Network Access via Physical Ports</t>
+  </si>
+  <si>
+    <t>Active network ports within accessible areas allow unauthorised devices to connect directly to the internal network, bypassing perimeter controls and enabling internal access, data exposure, and potential disruption.</t>
+  </si>
+  <si>
+    <t>Unattended Active User Sessions</t>
+  </si>
+  <si>
+    <t>Unlocked and unattended user sessions allow unauthorised individuals to access systems and data under a valid user identity, enabling data exposure, unauthorised actions, and loss of accountability.</t>
+  </si>
+  <si>
+    <t>Unauthorised Use of Removable Media</t>
+  </si>
+  <si>
+    <t>Unrestricted use of removable media and external interfaces allows unauthorised data extraction or introduction of files, increasing risk of data leakage and system compromise.</t>
+  </si>
+  <si>
+    <t>Uncontrolled Third-Party and Contractor Access</t>
+  </si>
+  <si>
+    <t>External personnel may be granted physical access without sufficient restriction, monitoring, or time-bound control, enabling unauthorised interaction with systems and potential data exposure or disruption.</t>
+  </si>
+  <si>
+    <t>Implement immediate administrative controls to restrict and monitor physical access to critical infrastructure.
+- Assign a Key Orderly responsible for daily opening/closing and basic security checks; report unsecured areas
+- Enforce closed-door practice for offices and infrastructure areas when not in use
+- Restrict access to infrastructure rooms to authorised personnel only, based on role and need
+- Require contractors to be escorted at all times within controlled areas
+- Establish basic staff awareness, including responsibility to identify, challenge (if safe), or report unknown individuals
+- Limit visibility and knowledge of critical infrastructure locations to authorised personnel</t>
+  </si>
+  <si>
+    <t>Establish formalised and accountable physical access control processes within the department.
+- Implement centralised key management, including secure key storage, mandatory sign-in/out, and maintained key register
+- Assign named ownership for all controlled areas and keys, with clear accountability for access and security
+- Introduce colour-coded ID badge system with defined access zones; enforce badge visibility at all times
+- Define and enforce controlled access zones for infrastructure and restricted areas
+- Develop and implement onboarding and offboarding procedures to issue and recover keys and ID badges
+- Establish basic access logging and periodic audits to maintain visibility and accountability
+- Define and document security policies and procedures for physical access control and expected staff behaviour
+- Implement incident reporting process for unauthorised access, lost keys, or security breaches</t>
+  </si>
+  <si>
+    <t>Implement enterprise-level physical security controls through infrastructure investment and dedicated security operations.
+- Construct secured perimeter including fencing, controlled entry/exit points, and a staffed guard house
+- Deploy access control systems (e.g., RFID badge access) across site entry points and critical buildings
+- Install CCTV surveillance covering perimeter, entry points, and critical infrastructure areas, with retained and reviewable footage
+- Employ security personnel for access control, visitor verification, and routine patrols (day and night)
+- Integrate access events and surveillance monitoring into a central security function for real-time visibility and response
+- Implement visitor management process at entry points, including identity verification and access logging
+- Establish physical security monitoring and incident response procedures, aligned with organisational security governance</t>
+  </si>
+  <si>
+    <t>Head of Facilities</t>
+  </si>
+  <si>
+    <t>Implement immediate administrative controls to restrict and monitor physical access to critical infrastructure, including:
+- Define authorised access per controlled area
+- Assign Key Orderly for daily opening/closing checks
+- Enforce closed-door policy for offices and infrastructure areas
+- Implement contractor escort requirement
+- Communicate staff responsibility to challenge/report unknown individuals</t>
+  </si>
+  <si>
+    <t>Key Actions:
+- Limit ports to known devices (port security / sticky MAC)
+- Disable and isolate unused ports (unused VLAN, no trunking)
+- Implement black hole VLAN for unknown or inactive ports
+- Enable basic link and MAC event logging
+- Define and label authorised connection points
+- Use DHCP lease review to identify unknown devices</t>
+  </si>
+  <si>
+    <t>Key Actions:
+- Enforce strict voice and data VLAN separation
+- Implement DHCP snooping (trusted uplinks only)
+- Enable Dynamic ARP Inspection (DAI)
+- Apply IP Source Guard (where supported)
+- Introduce centralised syslog monitoring
+- Tune port security violation behaviour (shutdown/restrict)
+- Establish port labelling and mapping standard
+- Introduce basic physical port deterrents
+- Implement quarantine VLAN for unknown devices</t>
+  </si>
+  <si>
+    <t>Key Actions:
+- Implement Network Access Control (NAC) platform
+- Enforce 802.1X authentication across all access ports
+- Introduce certificate-based authentication (EAP-TLS)
+- Enable device profiling and compliance validation
+- Implement dynamic segmentation (identity-based access)
+- Integrate network access with physical security systems
+- Deploy centralised SIEM for event correlation and detection
+- Upgrade access layer infrastructure to support enforcement</t>
+  </si>
+  <si>
+    <t>Tasks
+- Audit all access switch ports (identify active vs unused)
+- Disable and isolate unused ports (unused VLAN, no trunking)
+- Configure port security on active ports (sticky MAC, limit per port)
+- Create and apply black hole VLAN to unused/unknown ports
+- Enable basic logging (link up/down, MAC events) on switches
+- Define and label authorised user connection points
+- Review DHCP leases to identify unknown or unauthorised devices</t>
+  </si>
+  <si>
+    <t>Implement redundant routing capability at each campus through the introduction of a secondary router, providing automated failover for gateway services and improving resilience of inter-campus connectivity within current infrastructure constraints.</t>
+  </si>
+  <si>
+    <t>Procure, install, and configure a secondary router at each campus to provide gateway redundancy. Configure failover between routers and integrate with existing network infrastructure, accounting for limitations in physical connectivity and available transport paths.</t>
   </si>
 </sst>
 </file>
@@ -942,7 +1058,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -957,18 +1073,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1150,11 +1260,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1222,13 +1356,28 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1237,32 +1386,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1634,7 +1792,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48" style="4" customWidth="1"/>
     <col min="3" max="3" width="16.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.42578125" style="5" customWidth="1"/>
@@ -1646,11 +1804,11 @@
     <col min="11" max="11" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="67.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="63" style="4" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="4" customWidth="1"/>
-    <col min="17" max="17" width="58.5703125" style="4" customWidth="1"/>
-    <col min="18" max="18" width="30" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="90.28515625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="102.7109375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="102.28515625" style="4" customWidth="1"/>
+    <col min="17" max="17" width="88.140625" style="4" customWidth="1"/>
+    <col min="18" max="18" width="39.42578125" style="4" customWidth="1"/>
     <col min="19" max="19" width="33.85546875" style="4" customWidth="1"/>
     <col min="20" max="20" width="51.140625" style="5" customWidth="1"/>
     <col min="21" max="21" width="16.28515625" style="20" bestFit="1" customWidth="1"/>
@@ -1660,72 +1818,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="30" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="26" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="26" t="s">
+      <c r="N1" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="26" t="s">
+      <c r="P1" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="Q1" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="26" t="s">
+      <c r="R1" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="S1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="T1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="31"/>
-      <c r="V1" s="28" t="s">
+      <c r="U1" s="35"/>
+      <c r="V1" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="W1" s="34" t="s">
+      <c r="W1" s="27" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:23" s="8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="29"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="26"/>
       <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1744,109 +1902,107 @@
       <c r="K2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
       <c r="T2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="U2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="V2" s="29"/>
-      <c r="W2" s="35"/>
-    </row>
-    <row r="3" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="V2" s="26"/>
+      <c r="W2" s="28"/>
+    </row>
+    <row r="3" spans="1:23" ht="240" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2">
+        <f>F3*G3</f>
         <v>25</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="13">
-        <v>4</v>
-      </c>
-      <c r="G3" s="13">
-        <v>4</v>
-      </c>
-      <c r="H3" s="13">
-        <f t="shared" ref="H3:H14" si="0">F3*G3</f>
-        <v>16</v>
-      </c>
-      <c r="I3" s="13">
-        <v>4</v>
-      </c>
-      <c r="J3" s="13">
-        <v>4</v>
-      </c>
-      <c r="K3" s="13">
-        <f t="shared" ref="K3:K14" si="1">I3*J3</f>
-        <v>16</v>
-      </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13">
+      <c r="I3" s="2">
+        <v>5</v>
+      </c>
+      <c r="J3" s="2">
+        <v>5</v>
+      </c>
+      <c r="K3" s="2">
+        <f>I3*J3</f>
+        <v>25</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2">
         <v>1</v>
       </c>
-      <c r="N3" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="O3" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q3" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="R3" s="13" t="s">
+      <c r="N3" s="43"/>
+      <c r="O3" s="43" t="s">
+        <v>205</v>
+      </c>
+      <c r="P3" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q3" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="S3" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="T3" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="U3" s="24">
-        <v>46132</v>
-      </c>
-      <c r="V3" s="13" t="s">
+      <c r="S3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="T3" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="U3" s="19">
+        <v>46361</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="W3" s="17">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W3" s="19">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="210" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>139</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="F4" s="6">
         <v>4</v>
@@ -1855,34 +2011,32 @@
         <v>4</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" si="0"/>
+        <f>F4*G4</f>
         <v>16</v>
       </c>
       <c r="I4" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="6">
         <v>4</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f>I4*J4</f>
+        <v>16</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="P4" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q4" s="6" t="s">
-        <v>181</v>
+      <c r="N4" s="6"/>
+      <c r="O4" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>212</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>153</v>
@@ -1890,17 +2044,17 @@
       <c r="S4" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T4" s="7" t="s">
-        <v>190</v>
+      <c r="T4" s="44" t="s">
+        <v>213</v>
       </c>
       <c r="U4" s="17">
-        <v>46147</v>
+        <v>46361</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="W4" s="18">
-        <v>46133</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -1917,7 +2071,7 @@
         <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
@@ -1926,130 +2080,115 @@
         <v>5</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" si="0"/>
+        <f>F5*G5</f>
         <v>15</v>
       </c>
       <c r="I5" s="2">
         <v>3</v>
       </c>
       <c r="J5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <f>I5*J5</f>
+        <v>12</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2">
         <v>3</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="P5" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="R5" s="2" t="s">
+      <c r="N5" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="O5" s="41" t="s">
+        <v>193</v>
+      </c>
+      <c r="P5" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q5" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="R5" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="T5" s="23" t="s">
-        <v>186</v>
+      <c r="T5" s="40" t="s">
+        <v>215</v>
       </c>
       <c r="U5" s="19">
-        <v>46140</v>
+        <v>46361</v>
       </c>
       <c r="V5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="W5" s="19">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="6">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6">
+        <f>F6*G6</f>
+        <v>12</v>
+      </c>
+      <c r="I6" s="6">
+        <v>3</v>
+      </c>
+      <c r="J6" s="6">
+        <v>4</v>
+      </c>
+      <c r="K6" s="6">
+        <f>I6*J6</f>
+        <v>12</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6">
+        <v>4</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="W5" s="19">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3</v>
-      </c>
-      <c r="G6" s="4">
-        <v>5</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="I6" s="4">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4">
-        <v>5</v>
-      </c>
-      <c r="K6" s="4">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="M6" s="4">
-        <v>4</v>
-      </c>
-      <c r="N6" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="P6" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="T6" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="U6" s="20">
-        <v>46147</v>
-      </c>
-      <c r="V6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="W6" s="20">
-        <v>46168</v>
+      <c r="W6" s="18">
+        <v>46089</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>136</v>
@@ -2058,7 +2197,7 @@
         <v>139</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F7" s="13">
         <v>3</v>
@@ -2067,7 +2206,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="13">
-        <f t="shared" si="0"/>
+        <f>F7*G7</f>
         <v>12</v>
       </c>
       <c r="I7" s="13">
@@ -2077,7 +2216,7 @@
         <v>4</v>
       </c>
       <c r="K7" s="13">
-        <f t="shared" si="1"/>
+        <f>I7*J7</f>
         <v>12</v>
       </c>
       <c r="L7" s="13"/>
@@ -2100,75 +2239,63 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="E8" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="4">
         <v>3</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>4</v>
       </c>
-      <c r="H8" s="6">
-        <f t="shared" si="0"/>
+      <c r="H8" s="4">
+        <f>F8*G8</f>
         <v>12</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="4">
         <v>3</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="4">
         <v>4</v>
       </c>
-      <c r="K8" s="6">
-        <f t="shared" si="1"/>
+      <c r="K8" s="4">
+        <f>I8*J8</f>
         <v>12</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6">
-        <v>6</v>
-      </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="18"/>
-      <c r="V8" s="6" t="s">
+      <c r="V8" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="W8" s="18">
+      <c r="W8" s="20">
         <v>46089</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>136</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F9" s="2">
         <v>3</v>
@@ -2177,7 +2304,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="0"/>
+        <f>F9*G9</f>
         <v>12</v>
       </c>
       <c r="I9" s="2">
@@ -2187,13 +2314,11 @@
         <v>4</v>
       </c>
       <c r="K9" s="2">
-        <f t="shared" si="1"/>
+        <f>I9*J9</f>
         <v>12</v>
       </c>
       <c r="L9" s="2"/>
-      <c r="M9" s="2">
-        <v>7</v>
-      </c>
+      <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -2211,157 +2336,173 @@
     </row>
     <row r="10" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F10" s="4">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4">
         <v>3</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
+        <f>F10*G10</f>
+        <v>12</v>
+      </c>
+      <c r="I10" s="4">
         <v>4</v>
       </c>
-      <c r="H10" s="4">
-        <f t="shared" si="0"/>
+      <c r="J10" s="4">
+        <v>3</v>
+      </c>
+      <c r="K10" s="4">
+        <f>I10*J10</f>
         <v>12</v>
-      </c>
-      <c r="I10" s="4">
-        <v>3</v>
-      </c>
-      <c r="J10" s="4">
-        <v>4</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M10" s="4">
-        <v>8</v>
       </c>
       <c r="V10" s="4" t="s">
         <v>154</v>
       </c>
       <c r="W10" s="20">
-        <v>46089</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="F11" s="13">
+      <c r="E11" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2">
+        <f>F11*G11</f>
+        <v>12</v>
+      </c>
+      <c r="I11" s="2">
         <v>3</v>
       </c>
-      <c r="H11" s="13">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I11" s="13">
-        <v>3</v>
-      </c>
-      <c r="J11" s="13">
-        <v>3</v>
-      </c>
-      <c r="K11" s="13">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13">
-        <v>9</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="13" t="s">
+      <c r="J11" s="2">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <f>I11*J11</f>
+        <v>12</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="W11" s="17">
-        <v>46089</v>
+      <c r="W11" s="19">
+        <v>46151</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F12" s="4">
         <v>3</v>
       </c>
       <c r="G12" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>F12*G12</f>
+        <v>15</v>
       </c>
       <c r="I12" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K12" s="4">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="M12" s="4">
+        <f>I12*J12</f>
         <v>10</v>
       </c>
+      <c r="N12" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="P12" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="U12" s="20">
+        <v>46147</v>
+      </c>
       <c r="V12" s="4" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="W12" s="20">
-        <v>46089</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>137</v>
@@ -2370,7 +2511,7 @@
         <v>139</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F13" s="13">
         <v>3</v>
@@ -2379,7 +2520,7 @@
         <v>3</v>
       </c>
       <c r="H13" s="13">
-        <f t="shared" si="0"/>
+        <f>F13*G13</f>
         <v>9</v>
       </c>
       <c r="I13" s="13">
@@ -2389,7 +2530,7 @@
         <v>3</v>
       </c>
       <c r="K13" s="13">
-        <f t="shared" si="1"/>
+        <f>I13*J13</f>
         <v>9</v>
       </c>
       <c r="L13" s="13"/>
@@ -2411,112 +2552,136 @@
     </row>
     <row r="14" spans="1:23" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>139</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>F14*G14</f>
+        <v>9</v>
       </c>
       <c r="I14" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="4">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="T14" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="U14" s="20">
-        <v>46419</v>
+        <f>I14*J14</f>
+        <v>9</v>
       </c>
       <c r="V14" s="4" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="W14" s="20">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="3"/>
-      <c r="U15" s="19"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="19"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="13">
+        <v>3</v>
+      </c>
+      <c r="G15" s="13">
+        <v>3</v>
+      </c>
+      <c r="H15" s="6">
+        <f>F15*G15</f>
+        <v>9</v>
+      </c>
+      <c r="I15" s="13">
+        <v>3</v>
+      </c>
+      <c r="J15" s="13">
+        <v>3</v>
+      </c>
+      <c r="K15" s="13">
+        <f>I15*J15</f>
+        <v>9</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="W15" s="17">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="6">
+        <v>3</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3</v>
+      </c>
+      <c r="H16" s="6">
+        <f>F16*G16</f>
+        <v>9</v>
+      </c>
+      <c r="I16" s="6">
+        <v>3</v>
+      </c>
+      <c r="J16" s="6">
+        <v>3</v>
+      </c>
+      <c r="K16" s="6">
+        <f>I16*J16</f>
+        <v>9</v>
+      </c>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
@@ -2527,89 +2692,219 @@
       <c r="S16" s="6"/>
       <c r="T16" s="7"/>
       <c r="U16" s="18"/>
-      <c r="V16" s="6"/>
-      <c r="W16" s="18"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="3"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="19"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="V16" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="W16" s="18">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F17" s="13">
+        <v>4</v>
+      </c>
+      <c r="G17" s="13">
+        <v>4</v>
+      </c>
+      <c r="H17" s="6">
+        <f>F17*G17</f>
+        <v>16</v>
+      </c>
+      <c r="I17" s="13">
+        <v>2</v>
+      </c>
+      <c r="J17" s="13">
+        <v>4</v>
+      </c>
+      <c r="K17" s="13">
+        <f>I17*J17</f>
+        <v>8</v>
+      </c>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q17" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="R17" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="S17" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="U17" s="17">
+        <v>46143</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="W17" s="17">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+        <v>27</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="6">
+        <v>4</v>
+      </c>
+      <c r="G18" s="6">
+        <v>4</v>
+      </c>
+      <c r="H18" s="6">
+        <f>F18*G18</f>
+        <v>16</v>
+      </c>
+      <c r="I18" s="6">
+        <v>2</v>
+      </c>
+      <c r="J18" s="6">
+        <v>4</v>
+      </c>
+      <c r="K18" s="6">
+        <f>I18*J18</f>
+        <v>8</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="18"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="N18" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="P18" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="T18" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="U18" s="18">
+        <v>46147</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="W18" s="18">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="4">
+        <f>F19*G19</f>
+        <v>16</v>
+      </c>
+      <c r="I19" s="2">
+        <v>4</v>
+      </c>
+      <c r="J19" s="2">
+        <v>2</v>
+      </c>
+      <c r="K19" s="2">
+        <f>I19*J19</f>
+        <v>8</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="19"/>
+      <c r="N19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="U19" s="19">
+        <v>46419</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W19" s="19">
+        <v>46113</v>
+      </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
@@ -2648,7 +2943,6 @@
       <c r="E21" s="3"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -2702,7 +2996,6 @@
       <c r="E23" s="3"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -2756,7 +3049,6 @@
       <c r="E25" s="3"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -2810,7 +3102,6 @@
       <c r="E27" s="3"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -4853,16 +5144,10 @@
       <c r="W102" s="18"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:W14">
-    <sortCondition descending="1" ref="K3:K14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:W19">
+    <sortCondition descending="1" ref="K3:K19"/>
   </sortState>
   <mergeCells count="18">
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="R1:R2"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:E2"/>
@@ -4875,6 +5160,12 @@
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="L3:L1048576">
